--- a/data/trans_camb/IP16A03-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A03-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 0,15</t>
+          <t>-18,62; 0,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,63; 1,9</t>
+          <t>-17,83; 1,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 9,32</t>
+          <t>-14,22; 9,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 20,92</t>
+          <t>0,53; 22,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 17,21</t>
+          <t>-2,25; 18,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 22,72</t>
+          <t>-2,81; 22,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 7,95</t>
+          <t>-6,65; 8,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 7,05</t>
+          <t>-7,07; 6,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 11,39</t>
+          <t>-6,17; 11,04</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,11; 354,25</t>
+          <t>-73,59; 268,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-75,68; 419,95</t>
+          <t>-78,26; 257,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-83,27; 416,23</t>
+          <t>-83,3; 428,88</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 5,82</t>
+          <t>-7,6; 5,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 1,88</t>
+          <t>-9,46; 2,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 0,35</t>
+          <t>-11,19; 0,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,55; -6,12</t>
+          <t>-21,14; -6,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 1,58</t>
+          <t>-15,9; 3,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,09; -4,92</t>
+          <t>-20,51; -5,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,02; -2,39</t>
+          <t>-13,55; -2,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 0,33</t>
+          <t>-11,85; 0,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-13,94; -3,97</t>
+          <t>-13,56; -3,65</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,89; 479,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-90,46; 44,24</t>
+          <t>-100,0; 80,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -41,87</t>
+          <t>-100,0; -57,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-94,85; -31,93</t>
+          <t>-95,53; -27,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-91,52; 23,67</t>
+          <t>-91,29; 20,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -51,37</t>
+          <t>-100,0; -55,04</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 17,26</t>
+          <t>-1,67; 18,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 0,0</t>
+          <t>-14,35; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 5,1</t>
+          <t>-8,75; 5,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 9,61</t>
+          <t>-5,93; 12,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 3,55</t>
+          <t>-11,43; 3,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 3,74</t>
+          <t>-10,31; 3,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 11,26</t>
+          <t>-2,11; 11,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 0,85</t>
+          <t>-8,58; 0,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 3,4</t>
+          <t>-6,28; 3,24</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-94,62; —</t>
+          <t>-87,46; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 4,03</t>
+          <t>-10,96; 5,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 8,2</t>
+          <t>-11,92; 7,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,91; -0,0</t>
+          <t>-16,4; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,46; 3,33</t>
+          <t>-13,66; 3,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 13,7</t>
+          <t>-10,49; 12,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 4,47</t>
+          <t>-12,25; 4,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 1,82</t>
+          <t>-10,03; 1,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 6,87</t>
+          <t>-8,12; 6,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 0,52</t>
+          <t>-10,58; 0,59</t>
         </is>
       </c>
     </row>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-94,06; 210,4</t>
+          <t>-91,7; 251,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 109,18</t>
+          <t>-100,0; 91,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 309,37</t>
+          <t>-100,0; 182,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-91,29; 31,24</t>
+          <t>-91,11; 34,8</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 2,86</t>
+          <t>-5,49; 3,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,3; -0,57</t>
+          <t>-7,97; -0,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,28; -0,99</t>
+          <t>-8,24; -0,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 0,97</t>
+          <t>-7,83; 1,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 1,96</t>
+          <t>-6,8; 3,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 0,07</t>
+          <t>-8,41; 0,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 0,59</t>
+          <t>-5,69; 0,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,15; -0,17</t>
+          <t>-6,49; -0,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,04; -1,42</t>
+          <t>-7,11; -1,59</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-69,25; 90,41</t>
+          <t>-68,85; 107,12</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-93,58; -1,78</t>
+          <t>-92,15; 0,77</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-94,44; -0,94</t>
+          <t>-93,67; -9,51</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-81,08; 34,68</t>
+          <t>-80,01; 44,86</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-75,28; 48,75</t>
+          <t>-70,34; 75,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-83,19; 10,49</t>
+          <t>-83,04; 7,25</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-64,06; 15,17</t>
+          <t>-66,01; 11,72</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-74,82; -2,17</t>
+          <t>-75,59; 2,93</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-82,26; -27,05</t>
+          <t>-82,41; -29,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A03-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A03-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,62; 0,02</t>
+          <t>-18,5; 0,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,83; 1,26</t>
+          <t>-17,11; 1,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 9,51</t>
+          <t>-14,49; 10,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 22,07</t>
+          <t>0,66; 22,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 18,97</t>
+          <t>-2,39; 18,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 22,26</t>
+          <t>-2,44; 22,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 8,29</t>
+          <t>-6,37; 8,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 6,34</t>
+          <t>-7,38; 6,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 11,04</t>
+          <t>-6,58; 11,18</t>
         </is>
       </c>
     </row>
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-73,59; 268,15</t>
+          <t>-72,47; 300,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-78,26; 257,27</t>
+          <t>-83,21; 246,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-83,3; 428,88</t>
+          <t>-76,2; 365,81</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 5,63</t>
+          <t>-8,72; 5,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 2,86</t>
+          <t>-9,82; 2,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 0,35</t>
+          <t>-12,5; 0,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,14; -6,66</t>
+          <t>-20,59; -5,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 3,16</t>
+          <t>-16,65; 3,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,51; -5,41</t>
+          <t>-20,44; -4,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,55; -2,6</t>
+          <t>-12,58; -2,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 0,12</t>
+          <t>-11,14; 0,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-13,56; -3,65</t>
+          <t>-13,54; -3,97</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-90,89; 479,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 80,18</t>
+          <t>-100,0; 80,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -57,46</t>
+          <t>-100,0; -37,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-95,53; -27,93</t>
+          <t>-95,71; -26,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-91,29; 20,07</t>
+          <t>-90,84; 42,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -55,04</t>
+          <t>-100,0; -48,45</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 18,97</t>
+          <t>-3,53; 17,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,35; 0,0</t>
+          <t>-11,75; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 5,13</t>
+          <t>-8,67; 5,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 12,04</t>
+          <t>-5,91; 12,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 3,6</t>
+          <t>-11,87; 3,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 3,78</t>
+          <t>-11,56; 3,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 11,43</t>
+          <t>-3,03; 10,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 0,87</t>
+          <t>-8,85; 1,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 3,24</t>
+          <t>-6,35; 3,38</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-87,46; —</t>
+          <t>-75,37; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 5,03</t>
+          <t>-12,06; 4,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 7,19</t>
+          <t>-10,77; 6,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,4; 0,0</t>
+          <t>-16,2; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 3,37</t>
+          <t>-12,86; 3,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 12,46</t>
+          <t>-9,97; 12,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 4,36</t>
+          <t>-13,54; 4,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 1,58</t>
+          <t>-10,43; 1,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 6,15</t>
+          <t>-8,49; 6,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 0,59</t>
+          <t>-10,48; 0,83</t>
         </is>
       </c>
     </row>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-91,7; 251,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 91,95</t>
+          <t>-100,0; 96,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 182,0</t>
+          <t>-100,0; 222,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-91,11; 34,8</t>
+          <t>-90,97; 62,26</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 3,27</t>
+          <t>-5,67; 3,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,97; -0,52</t>
+          <t>-8,09; -0,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,24; -0,79</t>
+          <t>-8,55; -1,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 1,14</t>
+          <t>-7,75; 1,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 3,05</t>
+          <t>-6,85; 2,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 0,14</t>
+          <t>-8,58; 0,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 0,45</t>
+          <t>-5,7; 0,55</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,49; -0,31</t>
+          <t>-5,98; -0,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,11; -1,59</t>
+          <t>-7,14; -1,6</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-68,85; 107,12</t>
+          <t>-68,07; 96,96</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-92,15; 0,77</t>
+          <t>-94,06; -2,0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-93,67; -9,51</t>
+          <t>-93,9; -11,83</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-80,01; 44,86</t>
+          <t>-77,78; 29,58</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-70,34; 75,1</t>
+          <t>-70,59; 56,79</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-83,04; 7,25</t>
+          <t>-80,65; 9,86</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-66,01; 11,72</t>
+          <t>-67,46; 13,87</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-75,59; 2,93</t>
+          <t>-74,03; -0,06</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-82,41; -29,84</t>
+          <t>-82,06; -26,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A03-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A03-Edad-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
+          <t>Menores que consumieron medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9,46</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5,59</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-7,63</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-6,27</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-4,84</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9,46</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,59</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,19</t>
+          <t>-3,89</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>-0,09</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 0,05</t>
+          <t>0,25; 20,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 1,42</t>
+          <t>-2,49; 17,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 10,55</t>
+          <t>-4,81; 11,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 22,61</t>
+          <t>-18,47; 0,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 18,8</t>
+          <t>-17,63; 1,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 22,51</t>
+          <t>-13,9; 14,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 8,91</t>
+          <t>-5,45; 7,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 6,38</t>
+          <t>-6,61; 7,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 11,18</t>
+          <t>-7,05; 8,61</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>386,15%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>228,25%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>146,76%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-79,22%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-65,06%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-50,24%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>386,15%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>228,25%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>252,85%</t>
+          <t>-40,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>-1,53%</t>
         </is>
       </c>
     </row>
@@ -808,22 +808,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-72,47; 300,46</t>
+          <t>-66,11; 354,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-83,21; 246,85</t>
+          <t>-75,68; 419,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-76,2; 365,81</t>
+          <t>-85,18; 309,49</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-12,14</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-7,01</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-11,48</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,41</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-3,05</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,81</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-12,14</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-7,01</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-11,4</t>
+          <t>-3,82</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-7,91</t>
+          <t>-7,96</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 5,96</t>
+          <t>-20,55; -6,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 2,29</t>
+          <t>-15,86; 1,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 0,71</t>
+          <t>-19,88; -5,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,59; -5,4</t>
+          <t>-7,51; 5,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 3,06</t>
+          <t>-9,63; 1,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,44; -4,98</t>
+          <t>-11,07; 0,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,58; -2,18</t>
+          <t>-13,02; -2,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 0,42</t>
+          <t>-11,56; 0,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-13,54; -3,97</t>
+          <t>-13,89; -4,08</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-57,76%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-94,6%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-8,77%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-64,61%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-80,84%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-57,76%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-93,92%</t>
+          <t>-81,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-90,62%</t>
+          <t>-91,12%</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,46; 44,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; -48,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 80,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -37,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-95,71; -26,66</t>
+          <t>-94,85; -31,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-90,84; 42,96</t>
+          <t>-91,52; 23,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -48,45</t>
+          <t>-100,0; -55,62</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,26</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,14</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0,87</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>6,73</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-2,79</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,26</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,26</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,14</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,04</t>
+          <t>-1,09</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,69</t>
+          <t>-0,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 17,34</t>
+          <t>-5,94; 9,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 0,0</t>
+          <t>-11,71; 3,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 5,17</t>
+          <t>-11,89; 4,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 12,17</t>
+          <t>-3,26; 17,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 3,52</t>
+          <t>-16,18; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 3,78</t>
+          <t>-11,98; 3,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 10,35</t>
+          <t>-3,02; 11,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 1,06</t>
+          <t>-9,21; 0,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 3,38</t>
+          <t>-7,3; 2,92</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-39,08%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-29,93%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>241,16%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-9,29%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-39,08%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-35,82%</t>
+          <t>-39,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-24,14%</t>
+          <t>-34,01%</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-75,37; —</t>
+          <t>-94,62; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-4,81</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,75</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-2,52</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-3,43</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-2,46</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-4,94</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-4,81</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,73</t>
+          <t>-4,4</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-4,08</t>
+          <t>-3,36</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 4,98</t>
+          <t>-13,46; 3,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 6,91</t>
+          <t>-10,78; 13,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 0,0</t>
+          <t>-12,57; 4,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 3,75</t>
+          <t>-11,76; 4,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 12,06</t>
+          <t>-10,87; 8,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 4,58</t>
+          <t>-14,42; 1,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 1,2</t>
+          <t>-10,27; 1,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 6,47</t>
+          <t>-7,82; 6,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 0,83</t>
+          <t>-9,75; 1,46</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-66,32%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-10,31%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-34,73%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-57,89%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-41,52%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-83,39%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-66,32%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-10,31%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-37,62%</t>
+          <t>-74,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-61,2%</t>
+          <t>-50,43%</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-94,18; 222,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 96,2</t>
+          <t>-100,0; 109,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 222,75</t>
+          <t>-100,0; 309,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-90,97; 62,26</t>
+          <t>-86,77; 73,23</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-3,43</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-2,23</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-4,14</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,35</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-3,94</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-4,18</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-3,43</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-2,23</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,93</t>
+          <t>-3,99</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-4,1</t>
+          <t>-4,07</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 3,06</t>
+          <t>-7,95; 0,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,09; -0,59</t>
+          <t>-7,62; 1,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,55; -1,1</t>
+          <t>-8,83; -0,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 1,0</t>
+          <t>-5,81; 2,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 2,38</t>
+          <t>-8,3; -0,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 0,01</t>
+          <t>-7,88; -0,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 0,55</t>
+          <t>-5,39; 0,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,98; -0,26</t>
+          <t>-6,15; -0,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,14; -1,6</t>
+          <t>-7,02; -1,43</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-47,16%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-30,72%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-56,91%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-23,2%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-67,84%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-71,93%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-47,16%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-30,72%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-54,1%</t>
+          <t>-68,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-62,15%</t>
+          <t>-61,75%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-68,07; 96,96</t>
+          <t>-81,08; 34,68</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-94,06; -2,0</t>
+          <t>-75,28; 48,75</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-93,9; -11,83</t>
+          <t>-84,66; 3,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-77,78; 29,58</t>
+          <t>-69,25; 90,41</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-70,59; 56,79</t>
+          <t>-93,58; -1,78</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-80,65; 9,86</t>
+          <t>-93,91; 7,05</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-67,46; 13,87</t>
+          <t>-64,06; 15,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-74,03; -0,06</t>
+          <t>-74,82; -2,17</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-82,06; -26,89</t>
+          <t>-82,02; -21,23</t>
         </is>
       </c>
     </row>
